--- a/week-01/Ex4C_GTrends_marketing.xlsx
+++ b/week-01/Ex4C_GTrends_marketing.xlsx
@@ -8,20 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kendratyler\Documents\dataanalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9DC312E-8601-4847-9D32-75BBF8BD4FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A3A16330-59F4-4BB5-B440-46BDE232479C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3590" yWindow="500" windowWidth="15260" windowHeight="10980" activeTab="1" xr2:uid="{50885531-1D66-43EC-8A0D-B11FA44CBEA6}"/>
+    <workbookView xWindow="3590" yWindow="500" windowWidth="15260" windowHeight="10980" firstSheet="1" activeTab="4" xr2:uid="{50885531-1D66-43EC-8A0D-B11FA44CBEA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex4_more GTrends" sheetId="1" r:id="rId1"/>
-    <sheet name="By State" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId2"/>
+    <sheet name="By State" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="Sales Region lookup " sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
   <si>
     <t>Region</t>
   </si>
@@ -201,6 +204,48 @@
   </si>
   <si>
     <t>Breakup</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> South Dakota</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nebraska</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minnesota</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wisconsin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Michigan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Dakota </t>
+  </si>
+  <si>
+    <t xml:space="preserve">State </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Region </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamburger </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milkshake </t>
+  </si>
+  <si>
+    <t>Northwest</t>
+  </si>
+  <si>
+    <t>North Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Cental </t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Central </t>
   </si>
 </sst>
 </file>
@@ -1996,6 +2041,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD3CA97-B9BE-48B8-8D91-FAF7D4081EFF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5055DE3-FB51-482E-B5B3-EDD48AAEDE23}">
   <dimension ref="A1:AZ4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2656,4 +2710,207 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D078B5A-18B6-4D5A-8E65-A511698FD879}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBA3ED8D-7AE9-497A-8478-74E07320C62C}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D2">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D5">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="str">
+        <f>TRIM(A12)</f>
+        <v>North Dakota</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D6">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="str">
+        <f>TRIM(B12)</f>
+        <v>South Dakota</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="D7">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f>TRIM(C12)</f>
+        <v>Nebraska</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="D8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
+        <f>TRIM(D12)</f>
+        <v>Minnesota</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
+        <f>TRIM(E12)</f>
+        <v>Wisconsin</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="str">
+        <f>TRIM(F12)</f>
+        <v>Michigan</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>